--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/KENTUCKY_2012.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/KENTUCKY_2012.xlsx
@@ -2706,7 +2706,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C131">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C147">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C453">
@@ -9330,7 +9330,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C499">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C519">
@@ -10716,7 +10716,7 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>General Felipe _Ngeles</t>
+          <t>General Felipe Angeles</t>
         </is>
       </c>
       <c r="C576">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C802">
